--- a/서버정보/20260911_리소스배포_개발.xlsx
+++ b/서버정보/20260911_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F79D06-B3BB-4746-99BB-6FB53CC50147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9819CA6C-E2A5-4D31-A513-19BF4A93918C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="448">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2092,10 +2092,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>d-sec-mevrsol01-nic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2186,12 +2182,6 @@
   <si>
     <t>hazr-d-dis-clvadmap01</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-sec-mevrsol02-nic</t>
-  </si>
-  <si>
-    <t>d-sec-mevrsol03-nic</t>
   </si>
 </sst>
 </file>
@@ -9496,7 +9486,7 @@
         <v>420</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O59" s="1" t="str">
         <f t="shared" si="8"/>
@@ -9547,7 +9537,7 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C60" s="1" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
@@ -9560,13 +9550,13 @@
         <v>23</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I60" s="1">
         <v>2</v>
@@ -9581,10 +9571,10 @@
         <v>182</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O60" s="1" t="str">
         <f>SUBSTITUTE(F60,"hazr-","")&amp;"-osdisk"</f>
@@ -9613,10 +9603,10 @@
         <v>49</v>
       </c>
       <c r="Y60" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="Z60" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="Z60" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="AA60" s="1" t="b">
         <v>1</v>
@@ -9635,7 +9625,7 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="1" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
@@ -9648,13 +9638,13 @@
         <v>23</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I61" s="1">
         <v>2</v>
@@ -9669,10 +9659,10 @@
         <v>182</v>
       </c>
       <c r="M61" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="N61" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="O61" s="1" t="str">
         <f>SUBSTITUTE(F61,"hazr-","")&amp;"-osdisk"</f>
@@ -9704,7 +9694,7 @@
         <v>57</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA61" s="1" t="b">
         <v>1</v>
@@ -9723,7 +9713,7 @@
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C62" s="1" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
@@ -9736,10 +9726,10 @@
         <v>23</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>195</v>
@@ -9757,10 +9747,10 @@
         <v>182</v>
       </c>
       <c r="M62" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="N62" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="O62" s="1" t="str">
         <f>SUBSTITUTE(F62,"hazr-","")&amp;"-osdisk"</f>
@@ -9792,7 +9782,7 @@
         <v>57</v>
       </c>
       <c r="Z62" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA62" s="1" t="b">
         <v>1</v>
@@ -9811,7 +9801,7 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C63" s="1" t="str" cm="1">
         <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
@@ -9824,10 +9814,10 @@
         <v>23</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>195</v>
@@ -9845,10 +9835,10 @@
         <v>182</v>
       </c>
       <c r="M63" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="N63" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="O63" s="1" t="str">
         <f>SUBSTITUTE(F63,"hazr-","")&amp;"-osdisk"</f>
@@ -9880,7 +9870,7 @@
         <v>57</v>
       </c>
       <c r="Z63" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA63" s="1" t="b">
         <v>1</v>
@@ -9899,7 +9889,7 @@
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C64" s="1" t="str" cm="1">
         <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
@@ -9912,10 +9902,10 @@
         <v>23</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>195</v>
@@ -9933,10 +9923,10 @@
         <v>182</v>
       </c>
       <c r="M64" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="N64" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="O64" s="1" t="str">
         <f>SUBSTITUTE(F64,"hazr-","")&amp;"-osdisk"</f>
@@ -9968,7 +9958,7 @@
         <v>57</v>
       </c>
       <c r="Z64" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AA64" s="1" t="b">
         <v>1</v>
@@ -13055,7 +13045,7 @@
         <v>23</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G56" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13109,7 +13099,7 @@
         <v>23</v>
       </c>
       <c r="F57" s="24" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G57" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13163,7 +13153,7 @@
         <v>23</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G58" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13217,7 +13207,7 @@
         <v>23</v>
       </c>
       <c r="F59" s="24" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G59" s="17" t="str">
         <f t="shared" si="2"/>
@@ -13271,7 +13261,7 @@
         <v>23</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G60" s="16" t="str">
         <f t="shared" si="2"/>
@@ -13330,8 +13320,9 @@
     <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -15744,7 +15735,7 @@
         <v>50</v>
       </c>
       <c r="K65" s="32" t="str">
-        <f t="shared" ref="K65:K79" si="5">SUBSTITUTE($I65,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="K65:K80" si="5">SUBSTITUTE($I65,"hazr-","")&amp;"-nic"</f>
         <v>d-com-esnweb01-nic</v>
       </c>
       <c r="L65" s="33" t="s">
@@ -16014,7 +16005,7 @@
       <c r="J72" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K72" s="34" t="str">
+      <c r="K72" s="17" t="str">
         <f t="shared" si="5"/>
         <v>az-d-int-host2-nic</v>
       </c>
@@ -16052,7 +16043,7 @@
       <c r="J73" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="K73" s="32" t="str">
+      <c r="K73" s="16" t="str">
         <f t="shared" si="5"/>
         <v>az-d-int-host3-nic</v>
       </c>
@@ -16090,7 +16081,7 @@
       <c r="J74" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="K74" s="34" t="str">
+      <c r="K74" s="17" t="str">
         <f t="shared" si="5"/>
         <v>az-d-int-host4-nic</v>
       </c>
@@ -16128,7 +16119,7 @@
       <c r="J75" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="K75" s="32" t="str">
+      <c r="K75" s="16" t="str">
         <f t="shared" si="5"/>
         <v>d-if-edmsstr01-nic</v>
       </c>
@@ -16162,13 +16153,14 @@
         <v>59</v>
       </c>
       <c r="I76" s="36" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J76" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="K76" s="36" t="s">
-        <v>425</v>
+      <c r="K76" s="34" t="str">
+        <f t="shared" si="5"/>
+        <v>d-dis-clvweb01-nic</v>
       </c>
       <c r="L76" s="36" t="s">
         <v>341</v>
@@ -16199,12 +16191,12 @@
         <v>91</v>
       </c>
       <c r="I77" s="32" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J77" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="K77" s="32" t="str">
+      <c r="K77" s="16" t="str">
         <f t="shared" si="5"/>
         <v>d-dis-clvap01-nic</v>
       </c>
@@ -16237,13 +16229,14 @@
         <v>91</v>
       </c>
       <c r="I78" s="36" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J78" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="K78" s="36" t="s">
-        <v>449</v>
+      <c r="K78" s="34" t="str">
+        <f t="shared" si="5"/>
+        <v>d-dis-clvssrap01-nic</v>
       </c>
       <c r="L78" s="36" t="s">
         <v>341</v>
@@ -16274,12 +16267,12 @@
         <v>91</v>
       </c>
       <c r="I79" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J79" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="K79" s="32" t="str">
+      <c r="K79" s="16" t="str">
         <f t="shared" si="5"/>
         <v>d-dis-clvadmweb01-nic</v>
       </c>
@@ -16312,13 +16305,14 @@
         <v>91</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J80" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="K80" s="36" t="s">
-        <v>450</v>
+      <c r="K80" s="34" t="str">
+        <f t="shared" si="5"/>
+        <v>d-dis-clvadmap01-nic</v>
       </c>
       <c r="L80" s="36" t="s">
         <v>341</v>
@@ -16345,12 +16339,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -16494,6 +16482,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -16503,22 +16497,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16534,4 +16512,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>